--- a/Desafio 4 - Vale Refeição/Desafio 4 - Dados/ATIVOS.xlsx
+++ b/Desafio 4 - Vale Refeição/Desafio 4 - Dados/ATIVOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Cursos e Treinamentos\Cientista de Dados\Treinamento Python\I2A2\Desafios\Desafio 4 - Vale Refeição\Desafio 4 - Dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCA45BB-79D6-422E-A4BA-4E98B0116591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37642665-5BAC-457D-BCF0-6B593C2F5053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,17 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ATIVOS!$A$1:$E$1816</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -607,7 +616,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -618,6 +627,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -640,11 +655,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15016,7 +15033,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="833" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="1">
         <v>32473</v>
       </c>
@@ -23244,7 +23261,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1317" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1317" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1317" s="1">
         <v>34914</v>
       </c>
@@ -24808,20 +24825,20 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1409" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1409" s="1">
+    <row r="1409" spans="1:5" s="5" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1409" s="4">
         <v>35701</v>
       </c>
-      <c r="B1409" s="1">
-        <v>1410</v>
-      </c>
-      <c r="C1409" s="1" t="s">
+      <c r="B1409" s="4">
+        <v>1410</v>
+      </c>
+      <c r="C1409" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D1409" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1409" s="1" t="s">
+      <c r="D1409" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1409" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -31748,12 +31765,12 @@
   <autoFilter ref="A1:E1816" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="34914"/>
+        <filter val="32473"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="4">
+    <filterColumn colId="3">
       <filters>
-        <filter val="SINDPD SP - SIND.TRAB.EM PROC DADOS E EMPR.EMPRESAS PROC DADOS ESTADO DE SP."/>
+        <filter val="Férias"/>
       </filters>
     </filterColumn>
   </autoFilter>
